--- a/Litter_summary/Input/LitterCat.xlsx
+++ b/Litter_summary/Input/LitterCat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dvanavermaete\OneDrive - ILVO\R Code\Seafloor litter\LitterEMODnet-main\LitterEMODnet-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ilvo-my.sharepoint.com/personal/david_vanavermaete_ilvo_vlaanderen_be/Documents/R Code/TGML/LitterEMODnet-main/LitterEMODnet-main/Litter_summary/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E827778-0271-42E2-9E27-4B70F2CD0B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{7E827778-0271-42E2-9E27-4B70F2CD0B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEE3D884-814F-4B44-9CD6-1E3B1A553483}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="-1935" windowWidth="14610" windowHeight="17385" xr2:uid="{4444DFA5-EC68-4909-801E-CA836BACE683}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4444DFA5-EC68-4909-801E-CA836BACE683}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="308">
   <si>
     <t>G_class</t>
   </si>
@@ -942,6 +942,27 @@
   </si>
   <si>
     <t>other total</t>
+  </si>
+  <si>
+    <t>G178</t>
+  </si>
+  <si>
+    <t>G90</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>G189</t>
+  </si>
+  <si>
+    <t>Cables</t>
+  </si>
+  <si>
+    <t>Table Cloths</t>
+  </si>
+  <si>
+    <t>Jery cans from polymer</t>
   </si>
 </sst>
 </file>
@@ -1313,13 +1334,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A16C63E9-9E43-4F75-9A59-A0761238ED8E}">
-  <dimension ref="A1:C137"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C141"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>288</v>
       </c>
@@ -1341,7 +1362,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>289</v>
       </c>
@@ -1352,7 +1373,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1363,7 +1384,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1374,7 +1395,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1385,7 +1406,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1396,7 +1417,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1407,7 +1428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -1418,7 +1439,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -1429,7 +1450,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>193</v>
       </c>
@@ -1440,7 +1461,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1451,7 +1472,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1462,7 +1483,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>203</v>
       </c>
@@ -1473,7 +1494,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -1484,7 +1505,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1495,7 +1516,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>214</v>
       </c>
@@ -1506,7 +1527,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1517,7 +1538,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>196</v>
       </c>
@@ -1528,7 +1549,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>209</v>
       </c>
@@ -1539,7 +1560,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1550,7 +1571,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -1561,7 +1582,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -1572,7 +1593,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1583,7 +1604,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -1594,7 +1615,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1605,7 +1626,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1616,7 +1637,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1627,7 +1648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>217</v>
       </c>
@@ -1638,7 +1659,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>200</v>
       </c>
@@ -1649,7 +1670,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>215</v>
       </c>
@@ -1660,7 +1681,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>208</v>
       </c>
@@ -1671,7 +1692,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>218</v>
       </c>
@@ -1682,7 +1703,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -1693,7 +1714,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -1704,7 +1725,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -1715,7 +1736,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -1726,7 +1747,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>211</v>
       </c>
@@ -1737,7 +1758,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>204</v>
       </c>
@@ -1748,7 +1769,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>201</v>
       </c>
@@ -1759,7 +1780,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -1770,7 +1791,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -1781,7 +1802,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>114</v>
       </c>
@@ -1792,7 +1813,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -1803,7 +1824,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>293</v>
       </c>
@@ -1814,7 +1835,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1825,7 +1846,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>210</v>
       </c>
@@ -1836,7 +1857,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
@@ -1847,7 +1868,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -1858,7 +1879,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>212</v>
       </c>
@@ -1869,7 +1890,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -1880,7 +1901,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -1891,7 +1912,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>28</v>
       </c>
@@ -1902,7 +1923,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1913,7 +1934,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>205</v>
       </c>
@@ -1924,7 +1945,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>206</v>
       </c>
@@ -1935,7 +1956,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>7</v>
       </c>
@@ -1946,7 +1967,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>197</v>
       </c>
@@ -1957,7 +1978,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1968,7 +1989,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>202</v>
       </c>
@@ -1979,7 +2000,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -1990,7 +2011,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>199</v>
       </c>
@@ -2001,7 +2022,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>213</v>
       </c>
@@ -2012,7 +2033,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>10</v>
       </c>
@@ -2023,7 +2044,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -2034,7 +2055,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>216</v>
       </c>
@@ -2045,7 +2066,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -2056,7 +2077,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -2067,7 +2088,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>198</v>
       </c>
@@ -2078,7 +2099,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>207</v>
       </c>
@@ -2089,7 +2110,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -2100,7 +2121,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>219</v>
       </c>
@@ -2111,7 +2132,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -2122,7 +2143,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -2133,7 +2154,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -2144,7 +2165,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -2155,7 +2176,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>220</v>
       </c>
@@ -2166,7 +2187,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>221</v>
       </c>
@@ -2177,7 +2198,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>222</v>
       </c>
@@ -2188,7 +2209,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>223</v>
       </c>
@@ -2199,7 +2220,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>224</v>
       </c>
@@ -2210,7 +2231,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>225</v>
       </c>
@@ -2221,7 +2242,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>226</v>
       </c>
@@ -2232,7 +2253,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>227</v>
       </c>
@@ -2243,7 +2264,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>228</v>
       </c>
@@ -2254,7 +2275,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>229</v>
       </c>
@@ -2265,7 +2286,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>230</v>
       </c>
@@ -2276,7 +2297,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>231</v>
       </c>
@@ -2287,7 +2308,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>232</v>
       </c>
@@ -2298,7 +2319,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>233</v>
       </c>
@@ -2309,7 +2330,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>234</v>
       </c>
@@ -2320,7 +2341,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>235</v>
       </c>
@@ -2331,7 +2352,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>236</v>
       </c>
@@ -2342,7 +2363,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>237</v>
       </c>
@@ -2353,7 +2374,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>238</v>
       </c>
@@ -2364,7 +2385,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>239</v>
       </c>
@@ -2375,7 +2396,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>240</v>
       </c>
@@ -2386,7 +2407,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>241</v>
       </c>
@@ -2397,7 +2418,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>242</v>
       </c>
@@ -2408,7 +2429,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>243</v>
       </c>
@@ -2419,7 +2440,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>244</v>
       </c>
@@ -2430,7 +2451,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -2441,7 +2462,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>154</v>
       </c>
@@ -2452,7 +2473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>155</v>
       </c>
@@ -2463,7 +2484,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>156</v>
       </c>
@@ -2474,7 +2495,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>157</v>
       </c>
@@ -2485,7 +2506,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>158</v>
       </c>
@@ -2496,7 +2517,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>159</v>
       </c>
@@ -2507,7 +2528,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>160</v>
       </c>
@@ -2518,7 +2539,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>161</v>
       </c>
@@ -2529,7 +2550,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>162</v>
       </c>
@@ -2540,7 +2561,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>163</v>
       </c>
@@ -2551,7 +2572,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>181</v>
       </c>
@@ -2562,7 +2583,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>177</v>
       </c>
@@ -2573,7 +2594,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>164</v>
       </c>
@@ -2584,7 +2605,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>190</v>
       </c>
@@ -2595,7 +2616,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>171</v>
       </c>
@@ -2606,7 +2627,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>172</v>
       </c>
@@ -2617,7 +2638,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>173</v>
       </c>
@@ -2628,7 +2649,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>174</v>
       </c>
@@ -2639,7 +2660,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>175</v>
       </c>
@@ -2650,7 +2671,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>176</v>
       </c>
@@ -2661,7 +2682,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>187</v>
       </c>
@@ -2672,7 +2693,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>167</v>
       </c>
@@ -2683,7 +2704,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>168</v>
       </c>
@@ -2694,7 +2715,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>169</v>
       </c>
@@ -2705,7 +2726,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>170</v>
       </c>
@@ -2716,7 +2737,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>184</v>
       </c>
@@ -2727,7 +2748,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>178</v>
       </c>
@@ -2738,7 +2759,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>166</v>
       </c>
@@ -2749,7 +2770,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>165</v>
       </c>
@@ -2760,7 +2781,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>151</v>
       </c>
@@ -2771,7 +2792,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>149</v>
       </c>
@@ -2782,7 +2803,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>294</v>
       </c>
@@ -2793,7 +2814,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>295</v>
       </c>
@@ -2804,7 +2825,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>150</v>
       </c>
@@ -2815,7 +2836,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>296</v>
       </c>
@@ -2824,6 +2845,50 @@
       </c>
       <c r="C137" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>301</v>
+      </c>
+      <c r="B138" t="s">
+        <v>111</v>
+      </c>
+      <c r="C138" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>302</v>
+      </c>
+      <c r="B139" t="s">
+        <v>85</v>
+      </c>
+      <c r="C139" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s">
+        <v>77</v>
+      </c>
+      <c r="C140" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>304</v>
+      </c>
+      <c r="B141" t="s">
+        <v>112</v>
+      </c>
+      <c r="C141" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
